--- a/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt2_nucleos.xlsx
@@ -727,13 +727,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEF45B00-DDD4-4576-81FC-1B7C26032A22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94D45CA2-7A75-4BD0-A2C2-D566B2214C59}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A785ACF-8228-445D-B10D-14856DE0DE3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DEFFAB6-50D3-412C-B7DE-44D08FAD7DE9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB66C2E0-5B6D-416F-9989-FDF5902AB30C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6251189-5AE1-4210-9F3F-84037DF2B87C}"/>
 </file>